--- a/tests/workbooktests/workbooks/test_rounding.xlsx
+++ b/tests/workbooktests/workbooks/test_rounding.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDAA8440-5ACA-4A91-956C-B7FCFE480AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CFEBED-6504-4584-B6E1-C2C09DFC55EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="-20235" windowWidth="28800" windowHeight="18120" xr2:uid="{E6774CD2-6F6A-4DF6-B333-76067AC47810}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{E6774CD2-6F6A-4DF6-B333-76067AC47810}"/>
   </bookViews>
   <sheets>
     <sheet name="Rounding" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -125,7 +125,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,31 +492,31 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D4" s="1">
         <f ca="1">RAND()</f>
-        <v>0.95445634362234399</v>
+        <v>0.30179402277607459</v>
       </c>
       <c r="E4" s="1">
         <f ca="1">RAND()*10</f>
-        <v>6.4776044175699123</v>
+        <v>5.7801917136036973</v>
       </c>
       <c r="F4" s="1">
         <f ca="1">RAND()*100</f>
-        <v>21.992348677954777</v>
+        <v>31.120533972810605</v>
       </c>
       <c r="G4" s="1">
         <f ca="1">RAND()*1000</f>
-        <v>8.0896318741841</v>
+        <v>225.25467397206256</v>
       </c>
       <c r="H4" s="1">
         <f ca="1">RAND()*10000</f>
-        <v>7880.7904070752429</v>
+        <v>477.44629983555444</v>
       </c>
       <c r="I4" s="1">
         <f ca="1">RAND()*100000</f>
-        <v>42360.709194449795</v>
+        <v>84836.432650964678</v>
       </c>
       <c r="J4" s="1">
         <f ca="1">RAND()*1000000</f>
-        <v>112757.11924763398</v>
+        <v>859824.30752762512</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -526,185 +526,185 @@
       <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="str" cm="1">
-        <f t="array" ref="C5">_xll.qlRounding(B5,$B$2,$B$3)</f>
-        <v>欣[Book1]Rounding!R5C3UpRounding,A</v>
-      </c>
-      <c r="D5" s="1" cm="1">
+      <c r="C5" t="e" cm="1">
+        <f t="array" aca="1" ref="C5" ca="1">_xll.qlRounding(B5,$B$2,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">_xll.qlRoundingApply($C5,D$4)</f>
-        <v>0.96</v>
-      </c>
-      <c r="E5" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">_xll.qlRoundingApply($C5,E$4)</f>
-        <v>6.48</v>
-      </c>
-      <c r="F5" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">_xll.qlRoundingApply($C5,F$4)</f>
-        <v>22</v>
-      </c>
-      <c r="G5" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">_xll.qlRoundingApply($C5,G$4)</f>
-        <v>8.09</v>
-      </c>
-      <c r="H5" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">_xll.qlRoundingApply($C5,H$4)</f>
-        <v>7880.8</v>
-      </c>
-      <c r="I5" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">_xll.qlRoundingApply($C5,I$4)</f>
-        <v>42360.71</v>
-      </c>
-      <c r="J5" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J5" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">_xll.qlRoundingApply($C5,J$4)</f>
-        <v>112757.12</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" t="str" cm="1">
-        <f t="array" ref="C6">_xll.qlRounding(B6,$B$2,$B$3)</f>
-        <v>欣[Book1]Rounding!R6C3DownRounding,A</v>
-      </c>
-      <c r="D6" s="1" cm="1">
+      <c r="C6" t="e" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_xll.qlRounding(B6,$B$2,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">_xll.qlRoundingApply($C6,D$4)</f>
-        <v>0.95</v>
-      </c>
-      <c r="E6" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">_xll.qlRoundingApply($C6,E$4)</f>
-        <v>6.47</v>
-      </c>
-      <c r="F6" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">_xll.qlRoundingApply($C6,F$4)</f>
-        <v>21.99</v>
-      </c>
-      <c r="G6" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="G6" ca="1">_xll.qlRoundingApply($C6,G$4)</f>
-        <v>8.08</v>
-      </c>
-      <c r="H6" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">_xll.qlRoundingApply($C6,H$4)</f>
-        <v>7880.79</v>
-      </c>
-      <c r="I6" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">_xll.qlRoundingApply($C6,I$4)</f>
-        <v>42360.7</v>
-      </c>
-      <c r="J6" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J6" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">_xll.qlRoundingApply($C6,J$4)</f>
-        <v>112757.11</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" t="str" cm="1">
-        <f t="array" ref="C7">_xll.qlRounding(B7,$B$2,$B$3)</f>
-        <v>欣[Book1]Rounding!R7C3ClosestRounding,A</v>
-      </c>
-      <c r="D7" s="1" cm="1">
+      <c r="C7" t="e" cm="1">
+        <f t="array" aca="1" ref="C7" ca="1">_xll.qlRounding(B7,$B$2,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">_xll.qlRoundingApply($C7,D$4)</f>
-        <v>0.95</v>
-      </c>
-      <c r="E7" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">_xll.qlRoundingApply($C7,E$4)</f>
-        <v>6.48</v>
-      </c>
-      <c r="F7" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">_xll.qlRoundingApply($C7,F$4)</f>
-        <v>21.99</v>
-      </c>
-      <c r="G7" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">_xll.qlRoundingApply($C7,G$4)</f>
-        <v>8.09</v>
-      </c>
-      <c r="H7" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">_xll.qlRoundingApply($C7,H$4)</f>
-        <v>7880.79</v>
-      </c>
-      <c r="I7" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">_xll.qlRoundingApply($C7,I$4)</f>
-        <v>42360.71</v>
-      </c>
-      <c r="J7" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">_xll.qlRoundingApply($C7,J$4)</f>
-        <v>112757.12</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="str" cm="1">
-        <f t="array" ref="C8">_xll.qlRounding(B8,$B$2,$B$3)</f>
-        <v>欣[Book1]Rounding!R8C3CeilingTruncation,A</v>
-      </c>
-      <c r="D8" s="1" cm="1">
+      <c r="C8" t="e" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_xll.qlRounding(B8,$B$2,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">_xll.qlRoundingApply($C8,D$4)</f>
-        <v>0.95</v>
-      </c>
-      <c r="E8" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">_xll.qlRoundingApply($C8,E$4)</f>
-        <v>6.47</v>
-      </c>
-      <c r="F8" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">_xll.qlRoundingApply($C8,F$4)</f>
-        <v>21.99</v>
-      </c>
-      <c r="G8" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="G8" ca="1">_xll.qlRoundingApply($C8,G$4)</f>
-        <v>8.08</v>
-      </c>
-      <c r="H8" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">_xll.qlRoundingApply($C8,H$4)</f>
-        <v>7880.79</v>
-      </c>
-      <c r="I8" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">_xll.qlRoundingApply($C8,I$4)</f>
-        <v>42360.7</v>
-      </c>
-      <c r="J8" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">_xll.qlRoundingApply($C8,J$4)</f>
-        <v>112757.11</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="str" cm="1">
-        <f t="array" ref="C9">_xll.qlRounding(B9,$B$2,$B$3)</f>
-        <v>欣[Book1]Rounding!R9C3FloorTruncation,A</v>
-      </c>
-      <c r="D9" s="1" cm="1">
+      <c r="C9" t="e" cm="1">
+        <f t="array" aca="1" ref="C9" ca="1">_xll.qlRounding(B9,$B$2,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">_xll.qlRoundingApply($C9,D$4)</f>
-        <v>0.95</v>
-      </c>
-      <c r="E9" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">_xll.qlRoundingApply($C9,E$4)</f>
-        <v>6.48</v>
-      </c>
-      <c r="F9" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">_xll.qlRoundingApply($C9,F$4)</f>
-        <v>21.99</v>
-      </c>
-      <c r="G9" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">_xll.qlRoundingApply($C9,G$4)</f>
-        <v>8.09</v>
-      </c>
-      <c r="H9" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">_xll.qlRoundingApply($C9,H$4)</f>
-        <v>7880.79</v>
-      </c>
-      <c r="I9" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">_xll.qlRoundingApply($C9,I$4)</f>
-        <v>42360.71</v>
-      </c>
-      <c r="J9" s="1" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="1" t="e" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">_xll.qlRoundingApply($C9,J$4)</f>
-        <v>112757.12</v>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
